--- a/ZonasEscolares/excels/APURIMAC-ABANCAY-ABANCAY.xlsx
+++ b/ZonasEscolares/excels/APURIMAC-ABANCAY-ABANCAY.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/APURIMAC-ABANCAY-ABANCAY.xlsx
+++ b/ZonasEscolares/excels/APURIMAC-ABANCAY-ABANCAY.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>01 SANTA TERESITA DEL NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-13.6375</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-72.87569999999999</v>
-      </c>
-      <c r="I2" t="n">
-        <v>293</v>
-      </c>
-      <c r="J2" t="n">
-        <v>13</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-13.6375</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-72.8757</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>06 NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-13.62898</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-72.88558</v>
-      </c>
-      <c r="I3" t="n">
-        <v>220</v>
-      </c>
-      <c r="J3" t="n">
-        <v>10</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-13.62898</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-72.88558</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>199 DIVINA PROVIDENCIA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-13.6386</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-72.8783</v>
-      </c>
-      <c r="I4" t="n">
-        <v>220</v>
-      </c>
-      <c r="J4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-13.6386</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-72.8783</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>SANTA ROSA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-13.63765</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-72.88066000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>810</v>
-      </c>
-      <c r="J5" t="n">
-        <v>46</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-13.63765</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-72.88066</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>54004 FRAY ARMANDO BONIFAZ / FRAY ARMANDO BONIFAZ F.</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-13.634219</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-72.881638</v>
-      </c>
-      <c r="I6" t="n">
-        <v>942</v>
-      </c>
-      <c r="J6" t="n">
-        <v>56</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-13.634219</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-72.881638</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>54005 MIGUEL GRAU / MIGUEL GRAU</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-13.631085</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-72.881135</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2104</v>
-      </c>
-      <c r="J7" t="n">
-        <v>109</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-13.631085</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-72.881135</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>54006 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-13.633</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-72.8839</v>
-      </c>
-      <c r="I8" t="n">
-        <v>661</v>
-      </c>
-      <c r="J8" t="n">
-        <v>27</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-13.633</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-72.8839</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>54007 ESTHER ROBERTI GAMERO / ESTHER ROBERTI GAMERO</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-13.6381</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-72.8797</v>
-      </c>
-      <c r="I9" t="n">
-        <v>773</v>
-      </c>
-      <c r="J9" t="n">
-        <v>42</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-13.6381</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-72.8797</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>773</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>54008 DIVINO MAESTRO / SOR ANA DE LOS ANGELES</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-13.62898</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-72.88442000000001</v>
-      </c>
-      <c r="I10" t="n">
-        <v>372</v>
-      </c>
-      <c r="J10" t="n">
-        <v>25</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-13.62898</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-72.88442</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>54009 / VILLA GLORIA</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-13.6339</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-72.87050000000001</v>
-      </c>
-      <c r="I11" t="n">
-        <v>495</v>
-      </c>
-      <c r="J11" t="n">
-        <v>28</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-13.6339</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-72.8705</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>54010 / 663 / MUTTER IRENE AMEND</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-13.6371</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-72.88679999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>746</v>
-      </c>
-      <c r="J12" t="n">
-        <v>40</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-13.6371</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-72.8868</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>54043 CESAR ABRAHAM VALLEJO</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-13.64003</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-72.88531</v>
-      </c>
-      <c r="I13" t="n">
-        <v>433</v>
-      </c>
-      <c r="J13" t="n">
-        <v>19</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-13.64003</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-72.88531</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-13.632446</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-72.889786</v>
-      </c>
-      <c r="I14" t="n">
-        <v>510</v>
-      </c>
-      <c r="J14" t="n">
-        <v>25</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-13.632446</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-72.889786</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>54872 LA SALLE</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-13.640243</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-72.883045</v>
-      </c>
-      <c r="I15" t="n">
-        <v>809</v>
-      </c>
-      <c r="J15" t="n">
-        <v>38</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-13.640243</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-72.883045</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>809</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>55001 MANUEL JESUS SIERRA A. / 661 / FRANCISCO BOLOGNESI</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-13.63487</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-72.88079999999999</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1136</v>
-      </c>
-      <c r="J16" t="n">
-        <v>65</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-13.63487</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-72.8808</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1136</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>AURORA INES TEJADA</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-13.63647</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-72.87732</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1094</v>
-      </c>
-      <c r="J17" t="n">
-        <v>61</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-13.63647</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-72.87732</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1094</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>150 / 55003 LA VICTORIA / LA VICTORIA</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-13.631278</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-72.875269</v>
-      </c>
-      <c r="I18" t="n">
-        <v>702</v>
-      </c>
-      <c r="J18" t="n">
-        <v>39</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-13.631278</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-72.875269</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>INDUSTRIAL</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-13.638273</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-72.887922</v>
-      </c>
-      <c r="I19" t="n">
-        <v>508</v>
-      </c>
-      <c r="J19" t="n">
-        <v>38</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-13.638273</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-72.887922</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>AMERICA</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-13.636774</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-72.88104</v>
-      </c>
-      <c r="I20" t="n">
-        <v>573</v>
-      </c>
-      <c r="J20" t="n">
-        <v>36</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-13.636774</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-72.88104</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>JUAN PABLO II</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-13.63713</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-72.88063</v>
-      </c>
-      <c r="I21" t="n">
-        <v>210</v>
-      </c>
-      <c r="J21" t="n">
-        <v>19</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-13.63713</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-72.88063</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>SAN FRANCISCO SOLANO</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-13.62072</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-72.87641600000001</v>
-      </c>
-      <c r="I22" t="n">
-        <v>387</v>
-      </c>
-      <c r="J22" t="n">
-        <v>30</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-13.62072</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-72.876416</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>PITAGORAS</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-13.63736</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-72.88361</v>
-      </c>
-      <c r="I23" t="n">
-        <v>474</v>
-      </c>
-      <c r="J23" t="n">
-        <v>18</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-13.63736</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-72.88361</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>NIÑO MANUELITO</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-13.63498</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-72.87793000000001</v>
-      </c>
-      <c r="I24" t="n">
-        <v>4</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-13.63498</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-72.87793</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>EL MUNDO MAGICO DE BELEN</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-13.63598</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-72.87855</v>
-      </c>
-      <c r="I25" t="n">
-        <v>7</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-13.63598</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-72.87855</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>54003 NUESTRA SEÑORA DEL ROSARIO / NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-13.63739</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-72.88437</v>
-      </c>
-      <c r="I26" t="n">
-        <v>872</v>
-      </c>
-      <c r="J26" t="n">
-        <v>43</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-13.63739</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-72.88437</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>872</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>SEDE SAPIENTIAE</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-13.6385</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-72.88475</v>
-      </c>
-      <c r="I27" t="n">
-        <v>328</v>
-      </c>
-      <c r="J27" t="n">
-        <v>16</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-13.6385</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-72.88475</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>PITAGORAS</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-13.637347</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-72.878878</v>
-      </c>
-      <c r="I28" t="n">
-        <v>627</v>
-      </c>
-      <c r="J28" t="n">
-        <v>20</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-13.637347</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-72.878878</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-13.632446</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-72.889786</v>
-      </c>
-      <c r="I29" t="n">
-        <v>767</v>
-      </c>
-      <c r="J29" t="n">
-        <v>54</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-13.632446</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-72.889786</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>54043 CESAR ABRAHAM VALLEJO</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-13.64003</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-72.88531</v>
-      </c>
-      <c r="I30" t="n">
-        <v>414</v>
-      </c>
-      <c r="J30" t="n">
-        <v>22</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-13.64003</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-72.88531</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>SANTO DOMINGO DE GUZMAN</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-13.635471</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-72.874353</v>
-      </c>
-      <c r="I31" t="n">
-        <v>215</v>
-      </c>
-      <c r="J31" t="n">
-        <v>23</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-13.635471</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-72.874353</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/APURIMAC-ABANCAY-ABANCAY.xlsx
+++ b/ZonasEscolares/excels/APURIMAC-ABANCAY-ABANCAY.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>42081</t>
+          <t>42123</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01 SANTA TERESITA DEL NIÑO JESUS</t>
+          <t>06 NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-13.6375</t>
+          <t>-13.62898</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-72.8757</t>
+          <t>-72.88558</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>220</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,22 +563,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>42123</t>
+          <t>42279</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>06 NUESTRA SEÑORA DEL CARMEN</t>
+          <t>199 DIVINA PROVIDENCIA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-13.62898</t>
+          <t>-13.6386</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-72.88558</t>
+          <t>-72.8783</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>42279</t>
+          <t>42383</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>199 DIVINA PROVIDENCIA</t>
+          <t>54005 MIGUEL GRAU / MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-13.6386</t>
+          <t>-13.631085</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-72.8783</t>
+          <t>-72.881135</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>109</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>42335</t>
+          <t>42081</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SANTA ROSA</t>
+          <t>01 SANTA TERESITA DEL NIÑO JESUS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-13.63765</t>
+          <t>-13.6375</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-72.88066</t>
+          <t>-72.8757</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>293</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>42378</t>
+          <t>784001</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>54004 FRAY ARMANDO BONIFAZ / FRAY ARMANDO BONIFAZ F.</t>
+          <t>SEDE SAPIENTIAE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-13.634219</t>
+          <t>-13.6385</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-72.881638</t>
+          <t>-72.88475</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>328</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>42383</t>
+          <t>613448</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>54005 MIGUEL GRAU / MIGUEL GRAU</t>
+          <t>PITAGORAS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-13.631085</t>
+          <t>-13.63736</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-72.881135</t>
+          <t>-72.88361</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>474</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>42397</t>
+          <t>42482</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>54006 SAGRADO CORAZON DE JESUS</t>
+          <t>54043 CESAR ABRAHAM VALLEJO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-13.633</t>
+          <t>-13.64003</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-72.8839</t>
+          <t>-72.88531</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>433</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>42401</t>
+          <t>42745</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>54007 ESTHER ROBERTI GAMERO / ESTHER ROBERTI GAMERO</t>
+          <t>JUAN PABLO II</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-13.6381</t>
+          <t>-13.63713</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-72.8797</t>
+          <t>-72.88063</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>210</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,37 +997,37 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>42415</t>
+          <t>648669</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>54008 DIVINO MAESTRO / SOR ANA DE LOS ANGELES</t>
+          <t>EL MUNDO MAGICO DE BELEN</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-13.62898</t>
+          <t>-13.63598</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-72.88442</t>
+          <t>-72.87855</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>42420</t>
+          <t>857399</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>54009 / VILLA GLORIA</t>
+          <t>PITAGORAS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-13.6339</t>
+          <t>-13.637347</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-72.8705</t>
+          <t>-72.878878</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>627</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>42439</t>
+          <t>864408</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>54010 / 663 / MUTTER IRENE AMEND</t>
+          <t>54043 CESAR ABRAHAM VALLEJO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-13.6371</t>
+          <t>-13.64003</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-72.8868</t>
+          <t>-72.88531</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>414</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>42482</t>
+          <t>902207</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>54043 CESAR ABRAHAM VALLEJO</t>
+          <t>SANTO DOMINGO DE GUZMAN</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-13.64003</t>
+          <t>-13.635471</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-72.88531</t>
+          <t>-72.874353</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>215</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,27 +1245,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>42552</t>
+          <t>42415</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>54008 DIVINO MAESTRO / SOR ANA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-13.632446</t>
+          <t>-13.62898</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-72.889786</t>
+          <t>-72.88442</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>372</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>42613</t>
+          <t>42552</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>54872 LA SALLE</t>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-13.640243</t>
+          <t>-13.632446</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-72.883045</t>
+          <t>-72.889786</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>510</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>42632</t>
+          <t>42397</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>55001 MANUEL JESUS SIERRA A. / 661 / FRANCISCO BOLOGNESI</t>
+          <t>54006 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-13.63487</t>
+          <t>-13.633</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-72.8808</t>
+          <t>-72.8839</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>661</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>42646</t>
+          <t>42420</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AURORA INES TEJADA</t>
+          <t>54009 / VILLA GLORIA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-13.63647</t>
+          <t>-13.6339</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-72.87732</t>
+          <t>-72.8705</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>495</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,37 +1493,37 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>42651</t>
+          <t>646590</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>150 / 55003 LA VICTORIA / LA VICTORIA</t>
+          <t>NIÑO MANUELITO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-13.631278</t>
+          <t>-13.63498</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-72.875269</t>
+          <t>-72.87793</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>42689</t>
+          <t>44546</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>INDUSTRIAL</t>
+          <t>SAN FRANCISCO SOLANO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-13.638273</t>
+          <t>-13.62072</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-72.887922</t>
+          <t>-72.876416</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>387</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>42745</t>
+          <t>42613</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JUAN PABLO II</t>
+          <t>54872 LA SALLE</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-13.63713</t>
+          <t>-13.640243</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-72.88063</t>
+          <t>-72.883045</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>809</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>44546</t>
+          <t>42689</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO SOLANO</t>
+          <t>INDUSTRIAL</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-13.62072</t>
+          <t>-13.638273</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-72.876416</t>
+          <t>-72.887922</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>508</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>613448</t>
+          <t>42651</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PITAGORAS</t>
+          <t>150 / 55003 LA VICTORIA / LA VICTORIA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-13.63736</t>
+          <t>-13.631278</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-72.88361</t>
+          <t>-72.875269</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>702</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,37 +1865,37 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>646590</t>
+          <t>42439</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>NIÑO MANUELITO</t>
+          <t>54010 / 663 / MUTTER IRENE AMEND</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-13.63498</t>
+          <t>-13.6371</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-72.87793</t>
+          <t>-72.8868</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>746</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1927,37 +1927,37 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>648669</t>
+          <t>42401</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>EL MUNDO MAGICO DE BELEN</t>
+          <t>54007 ESTHER ROBERTI GAMERO / ESTHER ROBERTI GAMERO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-13.63598</t>
+          <t>-13.6381</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-72.87855</t>
+          <t>-72.8797</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>773</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>784001</t>
+          <t>42335</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SEDE SAPIENTIAE</t>
+          <t>SANTA ROSA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-13.6385</t>
+          <t>-13.63765</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-72.88475</t>
+          <t>-72.88066</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>810</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>857399</t>
+          <t>864385</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PITAGORAS</t>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-13.637347</t>
+          <t>-13.632446</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-72.878878</t>
+          <t>-72.889786</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>767</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>864385</t>
+          <t>42378</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>54004 FRAY ARMANDO BONIFAZ / FRAY ARMANDO BONIFAZ F.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-13.632446</t>
+          <t>-13.634219</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-72.889786</t>
+          <t>-72.881638</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>942</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>864408</t>
+          <t>42646</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>54043 CESAR ABRAHAM VALLEJO</t>
+          <t>AURORA INES TEJADA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-13.64003</t>
+          <t>-13.63647</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-72.88531</t>
+          <t>-72.87732</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>902207</t>
+          <t>42632</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO DE GUZMAN</t>
+          <t>55001 MANUEL JESUS SIERRA A. / 661 / FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-13.635471</t>
+          <t>-13.63487</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-72.874353</t>
+          <t>-72.8808</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">

--- a/ZonasEscolares/excels/APURIMAC-ABANCAY-ABANCAY.xlsx
+++ b/ZonasEscolares/excels/APURIMAC-ABANCAY-ABANCAY.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>42123</t>
+          <t>902207</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>06 NUESTRA SEÑORA DEL CARMEN</t>
+          <t>SANTO DOMINGO DE GUZMAN</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-13.62898</t>
+          <t>215</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-72.88558</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>-13.635471</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-72.874353</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>42279</t>
+          <t>864408</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>199 DIVINA PROVIDENCIA</t>
+          <t>54043 CESAR ABRAHAM VALLEJO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-13.6386</t>
+          <t>414</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-72.8783</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>-13.64003</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-72.88531</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>42383</t>
+          <t>864385</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>54005 MIGUEL GRAU / MIGUEL GRAU</t>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-13.631085</t>
+          <t>767</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-72.881135</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>-13.632446</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>-72.889786</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>42081</t>
+          <t>857399</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>01 SANTA TERESITA DEL NIÑO JESUS</t>
+          <t>PITAGORAS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-13.6375</t>
+          <t>627</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-72.8757</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>-13.637347</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-72.878878</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -759,22 +759,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>-13.6385</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>-72.88475</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>613448</t>
+          <t>779014</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PITAGORAS</t>
+          <t>54003 NUESTRA SEÑORA DEL ROSARIO / NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-13.63736</t>
+          <t>872</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-72.88361</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>-13.63739</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-72.88437</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>42482</t>
+          <t>648669</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>54043 CESAR ABRAHAM VALLEJO</t>
+          <t>EL MUNDO MAGICO DE BELEN</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-13.64003</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-72.88531</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>-13.63598</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-72.87855</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>42745</t>
+          <t>646590</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JUAN PABLO II</t>
+          <t>NIÑO MANUELITO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-13.63713</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-72.88063</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>-13.63498</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-72.87793</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,37 +997,37 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>648669</t>
+          <t>613448</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>EL MUNDO MAGICO DE BELEN</t>
+          <t>PITAGORAS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-13.63598</t>
+          <t>474</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-72.87855</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-13.63736</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-72.88361</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>857399</t>
+          <t>044546</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PITAGORAS</t>
+          <t>SAN FRANCISCO SOLANO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-13.637347</t>
+          <t>387</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-72.878878</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>-13.62072</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-72.876416</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>864408</t>
+          <t>042745</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>54043 CESAR ABRAHAM VALLEJO</t>
+          <t>JUAN PABLO II</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-13.64003</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-72.88531</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>-13.63713</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-72.88063</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>902207</t>
+          <t>042731</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO DE GUZMAN</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-13.635471</t>
+          <t>573</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-72.874353</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>-13.636774</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-72.88104</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>42415</t>
+          <t>042689</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>54008 DIVINO MAESTRO / SOR ANA DE LOS ANGELES</t>
+          <t>INDUSTRIAL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-13.62898</t>
+          <t>508</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-72.88442</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>-13.638273</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-72.887922</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>42552</t>
+          <t>042651</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>150 / 55003 LA VICTORIA / LA VICTORIA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-13.632446</t>
+          <t>702</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-72.889786</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>-13.631278</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-72.875269</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>42397</t>
+          <t>042646</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>54006 SAGRADO CORAZON DE JESUS</t>
+          <t>AURORA INES TEJADA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-13.633</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-72.8839</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>-13.63647</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-72.87732</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>42420</t>
+          <t>042632</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>54009 / VILLA GLORIA</t>
+          <t>55001 MANUEL JESUS SIERRA A. / 661 / FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-13.6339</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-72.8705</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>-13.63487</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-72.8808</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,37 +1493,37 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>646590</t>
+          <t>042613</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>NIÑO MANUELITO</t>
+          <t>54872 LA SALLE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-13.63498</t>
+          <t>809</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-72.87793</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-13.640243</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-72.883045</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>44546</t>
+          <t>042552</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO SOLANO</t>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-13.62072</t>
+          <t>510</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-72.876416</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>-13.632446</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-72.889786</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>42731</t>
+          <t>042482</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AMERICA</t>
+          <t>54043 CESAR ABRAHAM VALLEJO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-13.636774</t>
+          <t>433</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-72.88104</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>-13.64003</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-72.88531</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>42613</t>
+          <t>042439</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>54872 LA SALLE</t>
+          <t>54010 / 663 / MUTTER IRENE AMEND</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-13.640243</t>
+          <t>746</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-72.883045</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>-13.6371</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-72.8868</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>42689</t>
+          <t>042420</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>INDUSTRIAL</t>
+          <t>54009 / VILLA GLORIA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-13.638273</t>
+          <t>495</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-72.887922</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>-13.6339</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-72.8705</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>42651</t>
+          <t>042415</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>150 / 55003 LA VICTORIA / LA VICTORIA</t>
+          <t>54008 DIVINO MAESTRO / SOR ANA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-13.631278</t>
+          <t>372</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-72.875269</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>-13.62898</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-72.88442</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>42439</t>
+          <t>042401</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>54010 / 663 / MUTTER IRENE AMEND</t>
+          <t>54007 ESTHER ROBERTI GAMERO / ESTHER ROBERTI GAMERO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-13.6371</t>
+          <t>773</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-72.8868</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>-13.6381</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-72.8797</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>42401</t>
+          <t>042397</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>54007 ESTHER ROBERTI GAMERO / ESTHER ROBERTI GAMERO</t>
+          <t>54006 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-13.6381</t>
+          <t>661</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-72.8797</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>-13.633</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-72.8839</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>779014</t>
+          <t>042383</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>54003 NUESTRA SEÑORA DEL ROSARIO / NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>54005 MIGUEL GRAU / MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-13.63739</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-72.88437</t>
+          <t>109</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>-13.631085</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-72.881135</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>42335</t>
+          <t>042378</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SANTA ROSA</t>
+          <t>54004 FRAY ARMANDO BONIFAZ / FRAY ARMANDO BONIFAZ F.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-13.63765</t>
+          <t>942</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-72.88066</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>-13.634219</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-72.881638</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>864385</t>
+          <t>042335</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>SANTA ROSA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-13.632446</t>
+          <t>810</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-72.889786</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>-13.63765</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-72.88066</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>42378</t>
+          <t>042279</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>54004 FRAY ARMANDO BONIFAZ / FRAY ARMANDO BONIFAZ F.</t>
+          <t>199 DIVINA PROVIDENCIA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-13.634219</t>
+          <t>220</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-72.881638</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>-13.6386</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-72.8783</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>42646</t>
+          <t>042123</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AURORA INES TEJADA</t>
+          <t>06 NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-13.63647</t>
+          <t>220</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-72.87732</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>-13.62898</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>-72.88558</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>42632</t>
+          <t>042081</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>55001 MANUEL JESUS SIERRA A. / 661 / FRANCISCO BOLOGNESI</t>
+          <t>01 SANTA TERESITA DEL NIÑO JESUS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-13.63487</t>
+          <t>293</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-72.8808</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>-13.6375</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-72.8757</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">

--- a/ZonasEscolares/excels/APURIMAC-ABANCAY-ABANCAY.xlsx
+++ b/ZonasEscolares/excels/APURIMAC-ABANCAY-ABANCAY.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
